--- a/The_Saylor_Reflection.xlsx
+++ b/The_Saylor_Reflection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20eb409204932c1c/Lightning Bank Case Study/Yield_Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3516" documentId="13_ncr:1_{EAA91975-2987-4A27-8581-E5ECB033CA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C76FA40-CD5C-426B-9AA0-51489E530B89}"/>
+  <xr:revisionPtr revIDLastSave="3544" documentId="13_ncr:1_{EAA91975-2987-4A27-8581-E5ECB033CA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60D463B2-5689-46AC-97F0-8108DFBB9C48}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{10396A79-A4B2-467C-A467-ECE59C587EB2}"/>
   </bookViews>
@@ -230,7 +230,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;###0.00,,&quot; M&quot;"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -588,6 +588,21 @@
     <xf numFmtId="10" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -599,21 +614,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -991,24 +991,24 @@
   <sheetData>
     <row r="1" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="E2" s="51" t="s">
+      <c r="C2" s="55"/>
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="51"/>
+      <c r="F2" s="48"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="51"/>
+      <c r="L2" s="48"/>
       <c r="N2" s="17" t="s">
         <v>0</v>
       </c>
@@ -1016,29 +1016,29 @@
       <c r="Q2" s="28"/>
     </row>
     <row r="3" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="E3" s="53">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="E3" s="49">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F3" s="53"/>
+      <c r="F3" s="49"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="55">
+      <c r="H3" s="51">
         <v>104000</v>
       </c>
-      <c r="I3" s="55"/>
+      <c r="I3" s="51"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="55">
+      <c r="K3" s="51">
         <v>77000</v>
       </c>
-      <c r="L3" s="55"/>
+      <c r="L3" s="51"/>
       <c r="N3" s="18"/>
       <c r="P3" s="26"/>
       <c r="Q3" s="28"/>
     </row>
     <row r="4" spans="1:17" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1052,44 +1052,44 @@
       <c r="Q4" s="28"/>
     </row>
     <row r="5" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="E5" s="51" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="E5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="51"/>
+      <c r="F5" s="48"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="51"/>
+      <c r="I5" s="48"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="51"/>
+      <c r="L5" s="48"/>
       <c r="N5" s="3"/>
       <c r="P5" s="26"/>
       <c r="Q5" s="28"/>
     </row>
     <row r="6" spans="1:17" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="E6" s="53">
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="E6" s="49">
         <f>(K3/H3)^(1/DATEDIF(H6,K6,"Y"))-1</f>
         <v>-0.25961538461538458</v>
       </c>
-      <c r="F6" s="53"/>
+      <c r="F6" s="49"/>
       <c r="G6" s="6"/>
-      <c r="H6" s="54">
+      <c r="H6" s="50">
         <v>45794</v>
       </c>
-      <c r="I6" s="53"/>
+      <c r="I6" s="49"/>
       <c r="J6" s="6"/>
-      <c r="K6" s="54">
+      <c r="K6" s="50">
         <v>46159</v>
       </c>
-      <c r="L6" s="53"/>
+      <c r="L6" s="49"/>
       <c r="P6" s="26"/>
       <c r="Q6" s="28"/>
     </row>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="10" spans="1:17" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="9"/>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="52" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="F10" s="20">
         <f>E11</f>
-        <v>75309.52</v>
+        <v>77000</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -1217,13 +1217,14 @@
     </row>
     <row r="11" spans="1:17" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="9"/>
-      <c r="B11" s="48"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="19">
-        <v>75309.52</v>
+        <f>K3</f>
+        <v>77000</v>
       </c>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
@@ -1239,14 +1240,14 @@
     </row>
     <row r="12" spans="1:17" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="9"/>
-      <c r="B12" s="48"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="22">
         <f>IF(E10&gt;0&amp;E11&gt;0,E11/E10-1)</f>
-        <v>-0.27586999999999995</v>
+        <v>-0.25961538461538458</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
@@ -1262,14 +1263,14 @@
     </row>
     <row r="13" spans="1:17" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="9"/>
-      <c r="B13" s="48"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="22">
         <f>F$9/E$11-1</f>
-        <v>1.2980718772341131</v>
+        <v>1.2476193506493507</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
@@ -1285,14 +1286,14 @@
     </row>
     <row r="14" spans="1:17" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="9"/>
-      <c r="B14" s="49"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="24">
         <f>(F$9+(11.5%*E$10))/E$11-1</f>
-        <v>1.4568831404050906</v>
+        <v>1.4029440259740258</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -1402,7 +1403,7 @@
     </row>
     <row r="18" spans="1:35" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="9"/>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="52" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -1422,7 +1423,7 @@
     </row>
     <row r="19" spans="1:35" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9"/>
-      <c r="B19" s="48"/>
+      <c r="B19" s="53"/>
       <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
@@ -1440,7 +1441,7 @@
     </row>
     <row r="20" spans="1:35" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="9"/>
-      <c r="B20" s="48"/>
+      <c r="B20" s="53"/>
       <c r="C20" s="7" t="s">
         <v>12</v>
       </c>
@@ -1458,7 +1459,7 @@
     </row>
     <row r="21" spans="1:35" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="9"/>
-      <c r="B21" s="48"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="7" t="s">
         <v>13</v>
       </c>
@@ -1477,7 +1478,7 @@
     </row>
     <row r="22" spans="1:35" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="9"/>
-      <c r="B22" s="49"/>
+      <c r="B22" s="54"/>
       <c r="C22" s="15" t="s">
         <v>14</v>
       </c>
@@ -1495,6 +1496,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B2:C6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H5:I5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="H6:I6"/>
@@ -1505,11 +1511,6 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B2:C6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="H5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1619,62 +1620,62 @@
         <v>16</v>
       </c>
       <c r="C5" s="29">
-        <f>-$I$2</f>
+        <f t="shared" ref="C5:I5" si="0">-$I$2</f>
         <v>-0.115</v>
       </c>
       <c r="D5" s="29">
-        <f>-$I$2</f>
+        <f t="shared" si="0"/>
         <v>-0.115</v>
       </c>
       <c r="E5" s="29">
-        <f>-$I$2</f>
+        <f t="shared" si="0"/>
         <v>-0.115</v>
       </c>
       <c r="F5" s="29">
-        <f>-$I$2</f>
+        <f t="shared" si="0"/>
         <v>-0.115</v>
       </c>
       <c r="G5" s="29">
-        <f>-$I$2</f>
+        <f t="shared" si="0"/>
         <v>-0.115</v>
       </c>
       <c r="H5" s="29">
-        <f>-$I$2</f>
+        <f t="shared" si="0"/>
         <v>-0.115</v>
       </c>
       <c r="I5" s="29">
-        <f>-$I$2</f>
+        <f t="shared" si="0"/>
         <v>-0.115</v>
       </c>
       <c r="K5" s="33" t="s">
         <v>16</v>
       </c>
       <c r="L5" s="29">
-        <f>-$R$2</f>
+        <f t="shared" ref="L5:R5" si="1">-$R$2</f>
         <v>-0.13</v>
       </c>
       <c r="M5" s="29">
-        <f>-$R$2</f>
+        <f t="shared" si="1"/>
         <v>-0.13</v>
       </c>
       <c r="N5" s="29">
-        <f>-$R$2</f>
+        <f t="shared" si="1"/>
         <v>-0.13</v>
       </c>
       <c r="O5" s="29">
-        <f>-$R$2</f>
+        <f t="shared" si="1"/>
         <v>-0.13</v>
       </c>
       <c r="P5" s="29">
-        <f>-$R$2</f>
+        <f t="shared" si="1"/>
         <v>-0.13</v>
       </c>
       <c r="Q5" s="29">
-        <f>-$R$2</f>
+        <f t="shared" si="1"/>
         <v>-0.13</v>
       </c>
       <c r="R5" s="29">
-        <f>-$R$2</f>
+        <f t="shared" si="1"/>
         <v>-0.13</v>
       </c>
     </row>
@@ -1683,62 +1684,62 @@
         <v>18</v>
       </c>
       <c r="C6" s="35">
-        <f t="shared" ref="C6:I6" si="0">C4+C5</f>
+        <f t="shared" ref="C6:I6" si="2">C4+C5</f>
         <v>0.185</v>
       </c>
       <c r="D6" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.13500000000000001</v>
       </c>
       <c r="E6" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="F6" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.4999999999999989E-2</v>
       </c>
       <c r="G6" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1.4999999999999999E-2</v>
       </c>
       <c r="H6" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-6.5000000000000002E-2</v>
       </c>
       <c r="I6" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.115</v>
       </c>
       <c r="K6" s="32" t="s">
         <v>18</v>
       </c>
       <c r="L6" s="35">
-        <f t="shared" ref="L6:R6" si="1">L4+L5</f>
+        <f t="shared" ref="L6:R6" si="3">L4+L5</f>
         <v>0.16999999999999998</v>
       </c>
       <c r="M6" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
       <c r="N6" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O6" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.999999999999999E-2</v>
       </c>
       <c r="P6" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.03</v>
       </c>
       <c r="Q6" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.08</v>
       </c>
       <c r="R6" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.13</v>
       </c>
     </row>
@@ -1815,62 +1816,62 @@
         <v>16</v>
       </c>
       <c r="C9" s="39">
-        <f>-$I$2</f>
+        <f t="shared" ref="C9:I9" si="4">-$I$2</f>
         <v>-0.115</v>
       </c>
       <c r="D9" s="39">
-        <f>-$I$2</f>
+        <f t="shared" si="4"/>
         <v>-0.115</v>
       </c>
       <c r="E9" s="39">
-        <f>-$I$2</f>
+        <f t="shared" si="4"/>
         <v>-0.115</v>
       </c>
       <c r="F9" s="39">
-        <f>-$I$2</f>
+        <f t="shared" si="4"/>
         <v>-0.115</v>
       </c>
       <c r="G9" s="39">
-        <f>-$I$2</f>
+        <f t="shared" si="4"/>
         <v>-0.115</v>
       </c>
       <c r="H9" s="39">
-        <f>-$I$2</f>
+        <f t="shared" si="4"/>
         <v>-0.115</v>
       </c>
       <c r="I9" s="39">
-        <f>-$I$2</f>
+        <f t="shared" si="4"/>
         <v>-0.115</v>
       </c>
       <c r="K9" s="33" t="s">
         <v>16</v>
       </c>
       <c r="L9" s="39">
-        <f>-$R$2</f>
+        <f t="shared" ref="L9:R9" si="5">-$R$2</f>
         <v>-0.13</v>
       </c>
       <c r="M9" s="39">
-        <f>-$R$2</f>
+        <f t="shared" si="5"/>
         <v>-0.13</v>
       </c>
       <c r="N9" s="39">
-        <f>-$R$2</f>
+        <f t="shared" si="5"/>
         <v>-0.13</v>
       </c>
       <c r="O9" s="39">
-        <f>-$R$2</f>
+        <f t="shared" si="5"/>
         <v>-0.13</v>
       </c>
       <c r="P9" s="39">
-        <f>-$R$2</f>
+        <f t="shared" si="5"/>
         <v>-0.13</v>
       </c>
       <c r="Q9" s="39">
-        <f>-$R$2</f>
+        <f t="shared" si="5"/>
         <v>-0.13</v>
       </c>
       <c r="R9" s="39">
-        <f>-$R$2</f>
+        <f t="shared" si="5"/>
         <v>-0.13</v>
       </c>
     </row>
@@ -1883,27 +1884,27 @@
         <v>-0.16500000000000001</v>
       </c>
       <c r="D10" s="46">
-        <f t="shared" ref="D10:I10" si="2">D8+D9</f>
+        <f t="shared" ref="D10:I10" si="6">D8+D9</f>
         <v>-0.21500000000000002</v>
       </c>
       <c r="E10" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.26500000000000001</v>
       </c>
       <c r="F10" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.315</v>
       </c>
       <c r="G10" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.36499999999999999</v>
       </c>
       <c r="H10" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.41499999999999998</v>
       </c>
       <c r="I10" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-0.46499999999999997</v>
       </c>
       <c r="K10" s="44" t="s">
@@ -1914,27 +1915,27 @@
         <v>-0.18</v>
       </c>
       <c r="M10" s="46">
-        <f t="shared" ref="M10:R10" si="3">M8+M9</f>
+        <f t="shared" ref="M10:R10" si="7">M8+M9</f>
         <v>-0.23</v>
       </c>
       <c r="N10" s="46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.28000000000000003</v>
       </c>
       <c r="O10" s="46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.33</v>
       </c>
       <c r="P10" s="46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.38</v>
       </c>
       <c r="Q10" s="46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.43</v>
       </c>
       <c r="R10" s="46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.48</v>
       </c>
     </row>
@@ -1947,27 +1948,27 @@
         <v>5.2631578947368363E-2</v>
       </c>
       <c r="D11" s="37">
-        <f t="shared" ref="D11:I11" si="4">100/(100-(100*-D8))-1</f>
+        <f t="shared" ref="D11:I11" si="8">100/(100-(100*-D8))-1</f>
         <v>0.11111111111111116</v>
       </c>
       <c r="E11" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.17647058823529416</v>
       </c>
       <c r="F11" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
       <c r="G11" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.33333333333333326</v>
       </c>
       <c r="H11" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.4285714285714286</v>
       </c>
       <c r="I11" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.53846153846153855</v>
       </c>
       <c r="K11" s="14" t="s">
@@ -1982,23 +1983,23 @@
         <v>0.11111111111111116</v>
       </c>
       <c r="N11" s="37">
-        <f t="shared" ref="N11:R11" si="5">100/(100-(100*-N8))-1</f>
+        <f t="shared" ref="N11:R11" si="9">100/(100-(100*-N8))-1</f>
         <v>0.17647058823529416</v>
       </c>
       <c r="O11" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="P11" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.33333333333333326</v>
       </c>
       <c r="Q11" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.4285714285714286</v>
       </c>
       <c r="R11" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.53846153846153855</v>
       </c>
     </row>
@@ -2007,27 +2008,27 @@
         <v>20</v>
       </c>
       <c r="C12" s="39">
-        <f t="shared" ref="C12:H12" si="6">(100*(1-C9)/(100-(100*-C8))-1)-C11</f>
+        <f t="shared" ref="C12:H12" si="10">(100*(1-C9)/(100-(100*-C8))-1)-C11</f>
         <v>0.12105263157894752</v>
       </c>
       <c r="D12" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.12777777777777777</v>
       </c>
       <c r="E12" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.13529411764705879</v>
       </c>
       <c r="F12" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.14375000000000004</v>
       </c>
       <c r="G12" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.15333333333333332</v>
       </c>
       <c r="H12" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.16428571428571415</v>
       </c>
       <c r="I12" s="39">
@@ -2038,27 +2039,27 @@
         <v>20</v>
       </c>
       <c r="L12" s="39">
-        <f t="shared" ref="L12:Q12" si="7">(100*(1-L9)/(100-(100*-L8))-1)-L11</f>
+        <f t="shared" ref="L12:Q12" si="11">(100*(1-L9)/(100-(100*-L8))-1)-L11</f>
         <v>0.13684210526315788</v>
       </c>
       <c r="M12" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.14444444444444415</v>
       </c>
       <c r="N12" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.15294117647058814</v>
       </c>
       <c r="O12" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.16249999999999987</v>
       </c>
       <c r="P12" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.17333333333333312</v>
       </c>
       <c r="Q12" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.1857142857142855</v>
       </c>
       <c r="R12" s="39">
@@ -2075,27 +2076,27 @@
         <v>0.17368421052631589</v>
       </c>
       <c r="D13" s="37">
-        <f t="shared" ref="D13:I13" si="8">D11+D12</f>
+        <f t="shared" ref="D13:I13" si="12">D11+D12</f>
         <v>0.23888888888888893</v>
       </c>
       <c r="E13" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.31176470588235294</v>
       </c>
       <c r="F13" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.39375000000000004</v>
       </c>
       <c r="G13" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.48666666666666658</v>
       </c>
       <c r="H13" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.59285714285714275</v>
       </c>
       <c r="I13" s="37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.71538461538461529</v>
       </c>
       <c r="K13" s="14" t="s">
@@ -2106,27 +2107,27 @@
         <v>0.18947368421052624</v>
       </c>
       <c r="M13" s="37">
-        <f t="shared" ref="M13:R13" si="9">M11+M12</f>
+        <f t="shared" ref="M13:R13" si="13">M11+M12</f>
         <v>0.25555555555555531</v>
       </c>
       <c r="N13" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.32941176470588229</v>
       </c>
       <c r="O13" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.41249999999999987</v>
       </c>
       <c r="P13" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.50666666666666638</v>
       </c>
       <c r="Q13" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.6142857142857141</v>
       </c>
       <c r="R13" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.73846153846153828</v>
       </c>
     </row>
@@ -2189,62 +2190,62 @@
         <v>16</v>
       </c>
       <c r="C16" s="40">
-        <f>-$I$2</f>
+        <f t="shared" ref="C16:I16" si="14">-$I$2</f>
         <v>-0.115</v>
       </c>
       <c r="D16" s="40">
-        <f>-$I$2</f>
+        <f t="shared" si="14"/>
         <v>-0.115</v>
       </c>
       <c r="E16" s="40">
-        <f>-$I$2</f>
+        <f t="shared" si="14"/>
         <v>-0.115</v>
       </c>
       <c r="F16" s="40">
-        <f>-$I$2</f>
+        <f t="shared" si="14"/>
         <v>-0.115</v>
       </c>
       <c r="G16" s="40">
-        <f>-$I$2</f>
+        <f t="shared" si="14"/>
         <v>-0.115</v>
       </c>
       <c r="H16" s="40">
-        <f>-$I$2</f>
+        <f t="shared" si="14"/>
         <v>-0.115</v>
       </c>
       <c r="I16" s="40">
-        <f>-$I$2</f>
+        <f t="shared" si="14"/>
         <v>-0.115</v>
       </c>
       <c r="K16" s="33" t="s">
         <v>16</v>
       </c>
       <c r="L16" s="40">
-        <f>-$R$2</f>
+        <f t="shared" ref="L16:R16" si="15">-$R$2</f>
         <v>-0.13</v>
       </c>
       <c r="M16" s="40">
-        <f>-$R$2</f>
+        <f t="shared" si="15"/>
         <v>-0.13</v>
       </c>
       <c r="N16" s="40">
-        <f>-$R$2</f>
+        <f t="shared" si="15"/>
         <v>-0.13</v>
       </c>
       <c r="O16" s="40">
-        <f>-$R$2</f>
+        <f t="shared" si="15"/>
         <v>-0.13</v>
       </c>
       <c r="P16" s="40">
-        <f>-$R$2</f>
+        <f t="shared" si="15"/>
         <v>-0.13</v>
       </c>
       <c r="Q16" s="40">
-        <f>-$R$2</f>
+        <f t="shared" si="15"/>
         <v>-0.13</v>
       </c>
       <c r="R16" s="40">
-        <f>-$R$2</f>
+        <f t="shared" si="15"/>
         <v>-0.13</v>
       </c>
     </row>
@@ -2257,27 +2258,27 @@
         <v>-0.51500000000000001</v>
       </c>
       <c r="D17" s="45">
-        <f t="shared" ref="D17:I17" si="10">D15+D16</f>
+        <f t="shared" ref="D17:I17" si="16">D15+D16</f>
         <v>-0.56500000000000006</v>
       </c>
       <c r="E17" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-0.61499999999999999</v>
       </c>
       <c r="F17" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-0.66500000000000004</v>
       </c>
       <c r="G17" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-0.71499999999999997</v>
       </c>
       <c r="H17" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-0.76500000000000001</v>
       </c>
       <c r="I17" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-0.81499999999999995</v>
       </c>
       <c r="K17" s="44" t="s">
@@ -2288,27 +2289,27 @@
         <v>-0.53</v>
       </c>
       <c r="M17" s="45">
-        <f t="shared" ref="M17:R17" si="11">M15+M16</f>
+        <f t="shared" ref="M17:R17" si="17">M15+M16</f>
         <v>-0.58000000000000007</v>
       </c>
       <c r="N17" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>-0.63</v>
       </c>
       <c r="O17" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>-0.68</v>
       </c>
       <c r="P17" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>-0.73</v>
       </c>
       <c r="Q17" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>-0.78</v>
       </c>
       <c r="R17" s="45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>-0.83</v>
       </c>
     </row>
@@ -2321,27 +2322,27 @@
         <v>0.66666666666666674</v>
       </c>
       <c r="D18" s="38">
-        <f t="shared" ref="D18:I18" si="12">100/(100-(100*-D15))-1</f>
+        <f t="shared" ref="D18:I18" si="18">100/(100-(100*-D15))-1</f>
         <v>0.81818181818181812</v>
       </c>
       <c r="E18" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F18" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.2222222222222228</v>
       </c>
       <c r="G18" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.5</v>
       </c>
       <c r="H18" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.8571428571428572</v>
       </c>
       <c r="I18" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>2.3333333333333335</v>
       </c>
       <c r="K18" s="14" t="s">
@@ -2352,27 +2353,27 @@
         <v>0.66666666666666674</v>
       </c>
       <c r="M18" s="38">
-        <f t="shared" ref="M18:R18" si="13">100/(100-(100*-M15))-1</f>
+        <f t="shared" ref="M18:R18" si="19">100/(100-(100*-M15))-1</f>
         <v>0.81818181818181812</v>
       </c>
       <c r="N18" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O18" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>1.2222222222222228</v>
       </c>
       <c r="P18" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>1.5</v>
       </c>
       <c r="Q18" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>1.8571428571428572</v>
       </c>
       <c r="R18" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>2.3333333333333335</v>
       </c>
     </row>
@@ -2381,27 +2382,27 @@
         <v>20</v>
       </c>
       <c r="C19" s="40">
-        <f t="shared" ref="C19:H19" si="14">(100*(1-C16)/(100-(100*-C15))-1)-C18</f>
+        <f t="shared" ref="C19:H19" si="20">(100*(1-C16)/(100-(100*-C15))-1)-C18</f>
         <v>0.19166666666666665</v>
       </c>
       <c r="D19" s="40">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.20909090909090922</v>
       </c>
       <c r="E19" s="40">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="F19" s="40">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.25555555555555554</v>
       </c>
       <c r="G19" s="40">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.28750000000000009</v>
       </c>
       <c r="H19" s="40">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0.32857142857142829</v>
       </c>
       <c r="I19" s="40">
@@ -2412,27 +2413,27 @@
         <v>20</v>
       </c>
       <c r="L19" s="40">
-        <f t="shared" ref="L19:Q19" si="15">(100*(1-L16)/(100-(100*-L15))-1)-L18</f>
+        <f t="shared" ref="L19:Q19" si="21">(100*(1-L16)/(100-(100*-L15))-1)-L18</f>
         <v>0.21666666666666634</v>
       </c>
       <c r="M19" s="40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>0.23636363636363611</v>
       </c>
       <c r="N19" s="40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>0.25999999999999979</v>
       </c>
       <c r="O19" s="40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>0.28888888888888831</v>
       </c>
       <c r="P19" s="40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>0.32499999999999973</v>
       </c>
       <c r="Q19" s="40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>0.371428571428571</v>
       </c>
       <c r="R19" s="40">
@@ -2449,27 +2450,27 @@
         <v>0.85833333333333339</v>
       </c>
       <c r="D20" s="38">
-        <f t="shared" ref="D20:I20" si="16">D18+D19</f>
+        <f t="shared" ref="D20:I20" si="22">D18+D19</f>
         <v>1.0272727272727273</v>
       </c>
       <c r="E20" s="38">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>1.23</v>
       </c>
       <c r="F20" s="38">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>1.4777777777777783</v>
       </c>
       <c r="G20" s="38">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>1.7875000000000001</v>
       </c>
       <c r="H20" s="38">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.1857142857142855</v>
       </c>
       <c r="I20" s="38">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.7166666666666668</v>
       </c>
       <c r="K20" s="14" t="s">
@@ -2480,27 +2481,27 @@
         <v>0.88333333333333308</v>
       </c>
       <c r="M20" s="38">
-        <f t="shared" ref="M20:R20" si="17">M18+M19</f>
+        <f t="shared" ref="M20:R20" si="23">M18+M19</f>
         <v>1.0545454545454542</v>
       </c>
       <c r="N20" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1.2599999999999998</v>
       </c>
       <c r="O20" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1.5111111111111111</v>
       </c>
       <c r="P20" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>1.8249999999999997</v>
       </c>
       <c r="Q20" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>2.2285714285714282</v>
       </c>
       <c r="R20" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>2.7666666666666662</v>
       </c>
     </row>
